--- a/data/obx_xlsx/GOD.OL.xlsx
+++ b/data/obx_xlsx/GOD.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="481">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -844,6 +844,9 @@
   </si>
   <si>
     <t>Total Assets</t>
+  </si>
+  <si>
+    <t>Bank Loans Not use</t>
   </si>
   <si>
     <t>Bank Loans</t>
@@ -1589,7 +1592,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1668,6 +1671,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -11319,13 +11325,34 @@
       <c r="P42" s="19">
         <v>50.57</v>
       </c>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
+      <c r="Q42" s="18">
+        <f t="shared" ref="Q42:R42" si="1">Q43+Q51</f>
+        <v>47.33</v>
+      </c>
+      <c r="R42" s="18">
+        <f t="shared" si="1"/>
+        <v>24.73</v>
+      </c>
+      <c r="S42" s="18">
+        <f>S44+S52+S66</f>
+        <v>24.74</v>
+      </c>
+      <c r="T42" s="18">
+        <f t="shared" ref="T42:U42" si="2">T43+T51</f>
+        <v>11.08</v>
+      </c>
+      <c r="U42" s="18">
+        <f t="shared" si="2"/>
+        <v>8.88</v>
+      </c>
+      <c r="V42" s="18">
+        <f t="shared" ref="V42:W42" si="3">V44+V52</f>
+        <v>9.51</v>
+      </c>
+      <c r="W42" s="18">
+        <f t="shared" si="3"/>
+        <v>7.37</v>
+      </c>
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="13" t="s">
@@ -13552,7 +13579,7 @@
       </c>
     </row>
     <row r="97" ht="15.0" customHeight="1">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="27" t="s">
         <v>275</v>
       </c>
       <c r="B97" s="18"/>
@@ -13586,14 +13613,20 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B98" s="18"/>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
-      <c r="F98" s="18"/>
-      <c r="G98" s="18"/>
+      <c r="E98" s="19">
+        <v>44.42</v>
+      </c>
+      <c r="F98" s="19">
+        <v>44.35</v>
+      </c>
+      <c r="G98" s="19">
+        <v>35.28</v>
+      </c>
       <c r="H98" s="19">
         <v>34.92</v>
       </c>
@@ -13645,7 +13678,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B99" s="19">
         <v>27.1</v>
@@ -13716,7 +13749,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -13755,7 +13788,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
@@ -13808,7 +13841,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
@@ -13847,7 +13880,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B103" s="18"/>
       <c r="C103" s="18"/>
@@ -13910,7 +13943,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B104" s="19">
         <v>10.7</v>
@@ -13981,7 +14014,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B105" s="18"/>
       <c r="C105" s="18"/>
@@ -14010,7 +14043,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B106" s="18"/>
       <c r="C106" s="18"/>
@@ -14051,7 +14084,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B107" s="19">
         <v>29.3</v>
@@ -14096,7 +14129,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B108" s="14">
         <v>103.3</v>
@@ -14147,7 +14180,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B109" s="18"/>
       <c r="C109" s="19">
@@ -14178,7 +14211,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B110" s="18"/>
       <c r="C110" s="19">
@@ -14209,7 +14242,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B111" s="18"/>
       <c r="C111" s="19">
@@ -14240,7 +14273,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B112" s="18"/>
       <c r="C112" s="18"/>
@@ -14302,7 +14335,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B114" s="18">
         <v>0.0</v>
@@ -14335,7 +14368,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B115" s="19">
         <v>17.4</v>
@@ -14376,7 +14409,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B116" s="19">
         <v>0.1</v>
@@ -14415,7 +14448,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B117" s="18"/>
       <c r="C117" s="19">
@@ -14444,7 +14477,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B118" s="16">
         <v>187.9</v>
@@ -14515,7 +14548,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B119" s="18"/>
       <c r="C119" s="18"/>
@@ -14574,7 +14607,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B120" s="18"/>
       <c r="C120" s="18"/>
@@ -14633,7 +14666,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B121" s="18"/>
       <c r="C121" s="18"/>
@@ -14664,7 +14697,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B122" s="18">
         <v>0.0</v>
@@ -14721,7 +14754,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B123" s="18"/>
       <c r="C123" s="18"/>
@@ -14772,7 +14805,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B124" s="19">
         <v>45.6</v>
@@ -14813,7 +14846,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B125" s="18"/>
       <c r="C125" s="18"/>
@@ -14844,7 +14877,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B126" s="18"/>
       <c r="C126" s="18"/>
@@ -14877,7 +14910,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B127" s="18"/>
       <c r="C127" s="18"/>
@@ -14912,7 +14945,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B128" s="22">
         <v>45.6</v>
@@ -14983,7 +15016,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -15018,7 +15051,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B130" s="18"/>
       <c r="C130" s="18"/>
@@ -15053,7 +15086,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B131" s="16">
         <v>233.5</v>
@@ -15124,7 +15157,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B132" s="14">
         <v>503.9</v>
@@ -15177,7 +15210,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B133" s="19">
         <v>59.3</v>
@@ -15248,7 +15281,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B134" s="17">
         <v>-1.0</v>
@@ -15311,7 +15344,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B135" s="14">
         <v>445.6</v>
@@ -15368,7 +15401,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B136" s="18"/>
       <c r="C136" s="18"/>
@@ -15419,7 +15452,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -15450,7 +15483,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B138" s="26">
         <v>-226.9</v>
@@ -15521,7 +15554,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B139" s="18"/>
       <c r="C139" s="26">
@@ -15554,7 +15587,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B140" s="18"/>
       <c r="C140" s="19">
@@ -15601,7 +15634,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B141" s="18"/>
       <c r="C141" s="18"/>
@@ -15630,7 +15663,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B142" s="18"/>
       <c r="C142" s="18"/>
@@ -15661,7 +15694,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B143" s="16">
         <v>277.0</v>
@@ -15732,7 +15765,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B144" s="18"/>
       <c r="C144" s="18"/>
@@ -15901,7 +15934,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B147" s="16">
         <v>277.0</v>
@@ -15972,7 +16005,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B148" s="17">
         <v>-0.1</v>
@@ -16013,7 +16046,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B149" s="16">
         <v>510.4</v>
@@ -16084,7 +16117,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B150" s="19">
         <v>29.15</v>
@@ -16155,7 +16188,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B151" s="19">
         <v>0.48</v>
@@ -16226,7 +16259,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B152" s="19">
         <v>29.63</v>
@@ -16297,7 +16330,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -16338,7 +16371,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B154" s="18"/>
       <c r="C154" s="18"/>
@@ -16373,7 +16406,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B155" s="18"/>
       <c r="C155" s="18"/>
@@ -16408,7 +16441,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B156" s="18"/>
       <c r="C156" s="18"/>
@@ -16443,7 +16476,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B157" s="18"/>
       <c r="C157" s="18"/>
@@ -16496,7 +16529,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B158" s="18"/>
       <c r="C158" s="18"/>
@@ -16541,7 +16574,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B159" s="18"/>
       <c r="C159" s="18"/>
@@ -16586,7 +16619,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B160" s="18"/>
       <c r="C160" s="19">
@@ -16617,7 +16650,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B161" s="18"/>
       <c r="C161" s="19">
@@ -16648,7 +16681,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B162" s="18"/>
       <c r="C162" s="18"/>
@@ -16677,7 +16710,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B163" s="18"/>
       <c r="C163" s="19">
@@ -16708,7 +16741,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B164" s="18"/>
       <c r="C164" s="18"/>
@@ -16737,7 +16770,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B165" s="18"/>
       <c r="C165" s="19">
@@ -16768,7 +16801,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B166" s="18"/>
       <c r="C166" s="19">
@@ -16799,7 +16832,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B167" s="18"/>
       <c r="C167" s="17">
@@ -16828,7 +16861,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B168" s="19">
         <v>29.15</v>
@@ -16899,7 +16932,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B169" s="19">
         <v>0.48</v>
@@ -16970,7 +17003,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B170" s="19">
         <v>29.63</v>
@@ -17041,7 +17074,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B171" s="19">
         <v>1.0</v>
@@ -17960,7 +17993,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18346,75 +18379,75 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -18512,7 +18545,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B19" s="19">
         <v>9.0</v>
@@ -18574,7 +18607,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B21" s="17">
         <v>-0.3</v>
@@ -18613,7 +18646,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -18644,7 +18677,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -18683,7 +18716,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -18712,7 +18745,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -18743,7 +18776,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -18774,7 +18807,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -18805,7 +18838,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -18850,7 +18883,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -18893,7 +18926,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B30" s="19">
         <v>18.9</v>
@@ -19031,7 +19064,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -19096,7 +19129,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B33" s="19">
         <v>17.9</v>
@@ -19137,7 +19170,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B34" s="19">
         <v>4.0</v>
@@ -19204,7 +19237,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
@@ -19375,7 +19408,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B38" s="19">
         <v>0.4</v>
@@ -19442,7 +19475,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B39" s="19">
         <v>28.5</v>
@@ -19509,7 +19542,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B40" s="17">
         <v>-10.7</v>
@@ -19576,7 +19609,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B41" s="17">
         <v>-1.1</v>
@@ -19623,7 +19656,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B42" s="19">
         <v>3.4</v>
@@ -19676,7 +19709,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B43" s="17">
         <v>-3.6</v>
@@ -19745,7 +19778,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -19802,7 +19835,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
@@ -19833,7 +19866,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
@@ -19864,7 +19897,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -19895,7 +19928,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -19938,7 +19971,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B49" s="17">
         <v>-0.1</v>
@@ -19981,7 +20014,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" s="22">
         <v>83.1</v>
@@ -20052,7 +20085,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="19">
@@ -20109,7 +20142,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -20138,7 +20171,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="17">
@@ -20189,7 +20222,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B54" s="17">
         <v>-23.1</v>
@@ -20218,7 +20251,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -20259,7 +20292,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -20302,7 +20335,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
@@ -20335,7 +20368,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B58" s="17">
         <v>-3.5</v>
@@ -20402,7 +20435,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B59" s="17">
         <v>-2.8</v>
@@ -20469,7 +20502,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B60" s="19">
         <v>1.2</v>
@@ -20520,7 +20553,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -20555,7 +20588,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -20592,7 +20625,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
@@ -20621,7 +20654,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -20652,7 +20685,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
@@ -20689,7 +20722,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
@@ -20722,7 +20755,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B67" s="23">
         <v>-28.2</v>
@@ -20793,7 +20826,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -20836,7 +20869,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -20875,7 +20908,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B70" s="17">
         <v>-1.0</v>
@@ -20926,7 +20959,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
@@ -20979,7 +21012,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B72" s="17">
         <v>-17.5</v>
@@ -21024,7 +21057,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B73" s="17">
         <v>-21.0</v>
@@ -21067,7 +21100,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B74" s="19">
         <v>0.7</v>
@@ -21106,7 +21139,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -21135,7 +21168,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -21188,7 +21221,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B77" s="18"/>
       <c r="C77" s="18"/>
@@ -21223,7 +21256,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
@@ -21264,7 +21297,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
@@ -21303,7 +21336,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
@@ -21342,7 +21375,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B81" s="18"/>
       <c r="C81" s="18"/>
@@ -21379,7 +21412,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
@@ -21412,7 +21445,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
@@ -21447,7 +21480,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B84" s="19">
         <v>0.1</v>
@@ -21488,7 +21521,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B85" s="23">
         <v>-38.7</v>
@@ -21559,7 +21592,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B86" s="19">
         <v>0.2</v>
@@ -21628,7 +21661,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
@@ -21659,7 +21692,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B88" s="14">
         <v>110.8</v>
@@ -21730,7 +21763,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B89" s="14">
         <v>127.0</v>
@@ -21801,7 +21834,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B90" s="19">
         <v>16.1</v>
@@ -21858,7 +21891,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
@@ -21891,7 +21924,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B92" s="22">
         <v>16.4</v>
@@ -22889,7 +22922,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23059,22 +23092,22 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -23423,7 +23456,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -23521,3075 +23554,3075 @@
         <v>69</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Y18" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z18" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA18" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AB18" s="12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>429</v>
-      </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="28"/>
+      <c r="A19" s="28" t="s">
+        <v>430</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="29"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>429</v>
-      </c>
-      <c r="B20" s="30">
+      <c r="A20" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="B20" s="31">
         <v>258.37</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>249.07</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>225.46</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>270.15</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>289.2</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <v>165.36</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="32">
         <v>74.51</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
         <v>130.08</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="31">
         <v>134.37</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="31">
         <v>293.91</v>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="31">
         <v>569.43</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="31">
         <v>680.32</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="31">
         <v>435.71</v>
       </c>
-      <c r="O20" s="30">
+      <c r="O20" s="31">
         <v>652.85</v>
       </c>
-      <c r="P20" s="30">
+      <c r="P20" s="31">
         <v>681.53</v>
       </c>
-      <c r="Q20" s="30">
+      <c r="Q20" s="31">
         <v>262.65</v>
       </c>
-      <c r="R20" s="30">
+      <c r="R20" s="31">
         <v>216.25</v>
       </c>
-      <c r="S20" s="30">
+      <c r="S20" s="31">
         <v>503.1</v>
       </c>
-      <c r="T20" s="30">
+      <c r="T20" s="31">
         <v>515.89</v>
       </c>
-      <c r="U20" s="30">
+      <c r="U20" s="31">
         <v>151.81</v>
       </c>
-      <c r="V20" s="31">
+      <c r="V20" s="32">
         <v>37.33</v>
       </c>
-      <c r="W20" s="31">
+      <c r="W20" s="32">
         <v>62.55</v>
       </c>
-      <c r="X20" s="31">
+      <c r="X20" s="32">
         <v>1.19</v>
       </c>
-      <c r="Y20" s="31">
+      <c r="Y20" s="32">
         <v>39.12</v>
       </c>
-      <c r="Z20" s="31">
+      <c r="Z20" s="32">
         <v>49.52</v>
       </c>
-      <c r="AA20" s="30">
+      <c r="AA20" s="31">
         <v>165.0</v>
       </c>
-      <c r="AB20" s="30">
+      <c r="AB20" s="31">
         <v>161.06</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>430</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="B21" s="31">
         <v>258.45</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>239.85</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>204.94</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>185.86</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>158.7</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>159.65</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>240.46</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>361.62</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="31">
         <v>422.75</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>526.44</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>603.97</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>542.61</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>449.79</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>463.27</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="31">
         <v>435.88</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="31">
         <v>329.94</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>284.87</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>254.13</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="31">
         <v>153.75</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>58.4</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>37.94</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>63.47</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>83.18</v>
       </c>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="28"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28"/>
+      <c r="A22" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>431</v>
-      </c>
-      <c r="B23" s="30">
+      <c r="A23" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="B23" s="31">
         <v>294.27</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <v>284.57</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <v>216.34</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <v>255.97</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <v>305.58</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="31">
         <v>156.7</v>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="32">
         <v>87.84</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="31">
         <v>149.38</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="31">
         <v>160.13</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="31">
         <v>245.92</v>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="31">
         <v>390.35</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="31">
         <v>517.21</v>
       </c>
-      <c r="N23" s="30">
+      <c r="N23" s="31">
         <v>378.96</v>
       </c>
-      <c r="O23" s="30">
+      <c r="O23" s="31">
         <v>510.7</v>
       </c>
-      <c r="P23" s="30">
+      <c r="P23" s="31">
         <v>653.83</v>
       </c>
-      <c r="Q23" s="30">
+      <c r="Q23" s="31">
         <v>349.94</v>
       </c>
-      <c r="R23" s="30">
+      <c r="R23" s="31">
         <v>277.84</v>
       </c>
-      <c r="S23" s="30">
+      <c r="S23" s="31">
         <v>571.07</v>
       </c>
-      <c r="T23" s="30">
+      <c r="T23" s="31">
         <v>490.6</v>
       </c>
-      <c r="U23" s="30">
+      <c r="U23" s="31">
         <v>137.43</v>
       </c>
-      <c r="V23" s="31">
+      <c r="V23" s="32">
         <v>39.85</v>
       </c>
-      <c r="W23" s="31">
+      <c r="W23" s="32">
         <v>73.56</v>
       </c>
-      <c r="X23" s="31">
+      <c r="X23" s="32">
         <v>11.89</v>
       </c>
-      <c r="Y23" s="31">
+      <c r="Y23" s="32">
         <v>18.0</v>
       </c>
-      <c r="Z23" s="31">
+      <c r="Z23" s="32">
         <v>38.0</v>
       </c>
-      <c r="AA23" s="30">
+      <c r="AA23" s="31">
         <v>119.65</v>
       </c>
-      <c r="AB23" s="30">
+      <c r="AB23" s="31">
         <v>149.4</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>432</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="B24" s="31">
         <v>271.35</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>243.83</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>204.49</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>191.1</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>171.93</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>160.0</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>206.72</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>292.6</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="31">
         <v>338.51</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>408.63</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>490.21</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>482.13</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>434.26</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>472.68</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="31">
         <v>468.66</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="31">
         <v>365.38</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>303.36</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>262.5</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="31">
         <v>150.67</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>56.15</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>36.26</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>52.22</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>67.39</v>
       </c>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="32"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="27" t="s">
-        <v>433</v>
-      </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="28"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
+      <c r="A25" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="29"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>434</v>
-      </c>
-      <c r="B26" s="31">
+      <c r="A26" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="B26" s="32">
         <v>9.96</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <v>9.88</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="32">
         <v>7.8</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="32">
         <v>9.35</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="32">
         <v>11.3</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="32">
         <v>6.85</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="32">
         <v>3.84</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="32">
         <v>6.53</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="32">
         <v>7.0</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="32">
         <v>10.75</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="32">
         <v>12.0</v>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="32">
         <v>15.9</v>
       </c>
-      <c r="N26" s="31">
+      <c r="N26" s="32">
         <v>11.65</v>
       </c>
-      <c r="O26" s="31">
+      <c r="O26" s="32">
         <v>15.7</v>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="32">
         <v>20.1</v>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="32">
         <v>21.5</v>
       </c>
-      <c r="R26" s="31">
+      <c r="R26" s="32">
         <v>18.0</v>
       </c>
-      <c r="S26" s="31">
+      <c r="S26" s="32">
         <v>37.7</v>
       </c>
-      <c r="T26" s="31">
+      <c r="T26" s="32">
         <v>39.4</v>
       </c>
-      <c r="U26" s="31">
+      <c r="U26" s="32">
         <v>20.0</v>
       </c>
-      <c r="V26" s="31">
+      <c r="V26" s="32">
         <v>5.8</v>
       </c>
-      <c r="W26" s="31">
+      <c r="W26" s="32">
         <v>10.8</v>
       </c>
-      <c r="X26" s="31">
+      <c r="X26" s="32">
         <v>3.4</v>
       </c>
-      <c r="Y26" s="31">
+      <c r="Y26" s="32">
         <v>26.0</v>
       </c>
-      <c r="Z26" s="30">
+      <c r="Z26" s="31">
         <v>194.67</v>
       </c>
-      <c r="AA26" s="30">
+      <c r="AA26" s="31">
         <v>1022.5</v>
       </c>
-      <c r="AB26" s="30">
+      <c r="AB26" s="31">
         <v>1486.06</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>435</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" s="32">
         <v>9.66</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>9.04</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>7.83</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>7.57</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>7.1</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>6.99</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>8.02</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>10.44</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>11.46</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>13.2</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>15.07</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>16.97</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>17.39</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>22.6</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>27.34</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>27.32</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>24.18</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>22.74</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>15.88</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>13.2</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>48.13</v>
       </c>
-      <c r="W27" s="30">
+      <c r="W27" s="31">
         <v>251.47</v>
       </c>
-      <c r="X27" s="30">
+      <c r="X27" s="31">
         <v>546.53</v>
       </c>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="27" t="s">
-        <v>436</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="28"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
+      <c r="A28" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>437</v>
-      </c>
-      <c r="B29" s="33">
+      <c r="A29" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="B29" s="34">
         <v>-6.15</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="35">
         <v>24.78</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="35">
         <v>5.92</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <v>-2.25</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="35">
         <v>3.41</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="34">
         <v>-7.44</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="35">
         <v>2.67</v>
       </c>
-      <c r="I29" s="33">
+      <c r="I29" s="34">
         <v>-3.08</v>
       </c>
-      <c r="J29" s="33">
+      <c r="J29" s="34">
         <v>-11.21</v>
       </c>
-      <c r="K29" s="33">
+      <c r="K29" s="34">
         <v>-2.32</v>
       </c>
-      <c r="L29" s="33">
+      <c r="L29" s="34">
         <v>-13.09</v>
       </c>
-      <c r="M29" s="33">
+      <c r="M29" s="34">
         <v>-10.06</v>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="35">
         <v>28.75</v>
       </c>
-      <c r="O29" s="33">
+      <c r="O29" s="34">
         <v>-218.87</v>
       </c>
-      <c r="P29" s="34">
+      <c r="P29" s="35">
         <v>17.81</v>
       </c>
-      <c r="Q29" s="34">
+      <c r="Q29" s="35">
         <v>5.94</v>
       </c>
-      <c r="R29" s="34">
+      <c r="R29" s="35">
         <v>10.16</v>
       </c>
-      <c r="S29" s="34">
+      <c r="S29" s="35">
         <v>4.26</v>
       </c>
-      <c r="T29" s="33">
+      <c r="T29" s="34">
         <v>-2.48</v>
       </c>
-      <c r="U29" s="33">
+      <c r="U29" s="34">
         <v>-6.32</v>
       </c>
-      <c r="V29" s="33">
+      <c r="V29" s="34">
         <v>-17.23</v>
       </c>
-      <c r="W29" s="33">
+      <c r="W29" s="34">
         <v>-6.32</v>
       </c>
-      <c r="X29" s="33">
+      <c r="X29" s="34">
         <v>-108.03</v>
       </c>
-      <c r="Y29" s="33">
+      <c r="Y29" s="34">
         <v>-203.95</v>
       </c>
-      <c r="Z29" s="33">
+      <c r="Z29" s="34">
         <v>-125.59</v>
       </c>
-      <c r="AA29" s="33">
+      <c r="AA29" s="34">
         <v>-23.45</v>
       </c>
-      <c r="AB29" s="33">
+      <c r="AB29" s="34">
         <v>-39.35</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>438</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="B30" s="35">
         <v>5.12</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>5.7</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>0.59</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>-1.14</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>-2.84</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>-4.69</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>-6.74</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>-8.44</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>-1.49</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>-52.17</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>-40.62</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>-32.71</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>-27.98</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>-23.07</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>5.35</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>1.81</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>0.16</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>-2.04</v>
       </c>
-      <c r="T30" s="33">
+      <c r="T30" s="34">
         <v>-9.57</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="34">
         <v>-90.37</v>
       </c>
-      <c r="V30" s="33">
+      <c r="V30" s="34">
         <v>-125.85</v>
       </c>
-      <c r="W30" s="33">
+      <c r="W30" s="34">
         <v>-43.08</v>
       </c>
-      <c r="X30" s="33">
+      <c r="X30" s="34">
         <v>-41.2</v>
       </c>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="34"/>
-      <c r="AA30" s="34"/>
-      <c r="AB30" s="34"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="27" t="s">
-        <v>439</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
+      <c r="A31" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="29"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>440</v>
-      </c>
-      <c r="B32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="34">
+      <c r="A32" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="B32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="35">
         <v>3.95</v>
       </c>
-      <c r="M32" s="34">
+      <c r="M32" s="35">
         <v>6.79</v>
       </c>
-      <c r="N32" s="34">
+      <c r="N32" s="35">
         <v>4.94</v>
       </c>
-      <c r="O32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="34">
+      <c r="O32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="35">
         <v>5.37</v>
       </c>
-      <c r="Q32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="R32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="S32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="T32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="U32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="V32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="W32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="X32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Y32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Z32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="AA32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="AB32" s="34">
+      <c r="Q32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="R32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="S32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="T32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="U32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="V32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="W32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="X32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Y32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Z32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="AA32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="AB32" s="35">
         <v>0.0</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>441</v>
-      </c>
-      <c r="B33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="34">
+      <c r="A33" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="B33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="35">
         <v>1.18</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>2.98</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>3.72</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>3.23</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>4.26</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <v>3.22</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="35">
         <v>1.9</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="35">
         <v>0.96</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="35">
         <v>0.79</v>
       </c>
-      <c r="Q33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="R33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="S33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="T33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="U33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="V33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="W33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="X33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Y33" s="34"/>
-      <c r="Z33" s="34"/>
-      <c r="AA33" s="34"/>
-      <c r="AB33" s="34"/>
+      <c r="Q33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="R33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="S33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="T33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="U33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="V33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="W33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="X33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35"/>
+      <c r="AA33" s="35"/>
+      <c r="AB33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="B34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="34">
+      <c r="A34" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="B34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="35">
         <v>5.42</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="35">
         <v>9.43</v>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="35">
         <v>6.87</v>
       </c>
-      <c r="O34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="34">
+      <c r="O34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="35">
         <v>7.46</v>
       </c>
-      <c r="Q34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="R34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="S34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="T34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="U34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="V34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="W34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="X34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Y34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Z34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="AA34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="AB34" s="34">
+      <c r="Q34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="R34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="S34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="T34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="U34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="V34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="W34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="X34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Y34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Z34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="AA34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="AB34" s="35">
         <v>0.0</v>
       </c>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>443</v>
-      </c>
-      <c r="B35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="34">
+      <c r="A35" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="35">
         <v>1.62</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>4.12</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>5.15</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>4.47</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>5.91</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>4.48</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <v>2.65</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="35">
         <v>1.33</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="35">
         <v>1.1</v>
       </c>
-      <c r="Q35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="R35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="S35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="T35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="U35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="V35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="W35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="X35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="34"/>
-      <c r="AA35" s="34"/>
-      <c r="AB35" s="34"/>
+      <c r="Q35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="R35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="S35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="T35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="U35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="V35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="W35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="X35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AA35" s="35"/>
+      <c r="AB35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="27" t="s">
-        <v>444</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
+      <c r="A36" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+      <c r="W36" s="29"/>
+      <c r="X36" s="29"/>
+      <c r="Y36" s="29"/>
+      <c r="Z36" s="29"/>
+      <c r="AA36" s="29"/>
+      <c r="AB36" s="29"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>445</v>
-      </c>
-      <c r="B37" s="31">
+      <c r="A37" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="B37" s="32">
         <v>1.06</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="32">
         <v>0.98</v>
       </c>
-      <c r="D37" s="31">
+      <c r="D37" s="32">
         <v>0.81</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="32">
         <v>0.98</v>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="32">
         <v>1.11</v>
       </c>
-      <c r="G37" s="31">
+      <c r="G37" s="32">
         <v>0.68</v>
       </c>
-      <c r="H37" s="31">
+      <c r="H37" s="32">
         <v>0.37</v>
       </c>
-      <c r="I37" s="31">
+      <c r="I37" s="32">
         <v>0.5</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="32">
         <v>0.51</v>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="32">
         <v>0.72</v>
       </c>
-      <c r="L37" s="31">
+      <c r="L37" s="32">
         <v>0.57</v>
       </c>
-      <c r="M37" s="31">
+      <c r="M37" s="32">
         <v>0.71</v>
       </c>
-      <c r="N37" s="31">
+      <c r="N37" s="32">
         <v>0.55</v>
       </c>
-      <c r="O37" s="31">
+      <c r="O37" s="32">
         <v>0.77</v>
       </c>
-      <c r="P37" s="31">
+      <c r="P37" s="32">
         <v>1.0</v>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="32">
         <v>0.94</v>
       </c>
-      <c r="R37" s="31">
+      <c r="R37" s="32">
         <v>0.81</v>
       </c>
-      <c r="S37" s="31">
+      <c r="S37" s="32">
         <v>1.94</v>
       </c>
-      <c r="T37" s="31">
+      <c r="T37" s="32">
         <v>3.51</v>
       </c>
-      <c r="U37" s="31">
+      <c r="U37" s="32">
         <v>2.22</v>
       </c>
-      <c r="V37" s="31">
+      <c r="V37" s="32">
         <v>2.15</v>
       </c>
-      <c r="W37" s="31">
+      <c r="W37" s="32">
         <v>3.58</v>
       </c>
-      <c r="X37" s="32"/>
-      <c r="Y37" s="32"/>
-      <c r="Z37" s="32"/>
-      <c r="AA37" s="31">
+      <c r="X37" s="33"/>
+      <c r="Y37" s="33"/>
+      <c r="Z37" s="33"/>
+      <c r="AA37" s="32">
         <v>2.63</v>
       </c>
-      <c r="AB37" s="31">
+      <c r="AB37" s="32">
         <v>1.76</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>446</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="B38" s="32">
         <v>0.99</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>0.91</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>0.79</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>0.71</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>0.62</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>0.56</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>0.55</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>0.61</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>0.61</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>0.66</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>0.72</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>0.79</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>0.81</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>1.08</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>1.43</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>1.61</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>1.87</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>2.51</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>3.06</v>
       </c>
-      <c r="U38" s="32"/>
-      <c r="V38" s="32"/>
-      <c r="W38" s="31">
+      <c r="U38" s="33"/>
+      <c r="V38" s="33"/>
+      <c r="W38" s="32">
         <v>4.15</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>2.38</v>
       </c>
-      <c r="Y38" s="32"/>
-      <c r="Z38" s="32"/>
-      <c r="AA38" s="32"/>
-      <c r="AB38" s="32"/>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="27" t="s">
-        <v>447</v>
-      </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
+      <c r="A39" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+      <c r="W39" s="29"/>
+      <c r="X39" s="29"/>
+      <c r="Y39" s="29"/>
+      <c r="Z39" s="29"/>
+      <c r="AA39" s="29"/>
+      <c r="AB39" s="29"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>448</v>
-      </c>
-      <c r="B40" s="31">
+      <c r="A40" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="B40" s="32">
         <v>3.04</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="32">
         <v>2.65</v>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="32">
         <v>2.2</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="32">
         <v>2.65</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="32">
         <v>2.43</v>
       </c>
-      <c r="G40" s="31">
+      <c r="G40" s="32">
         <v>1.96</v>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="32">
         <v>1.05</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="32">
         <v>1.08</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J40" s="32">
         <v>1.08</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K40" s="32">
         <v>1.73</v>
       </c>
-      <c r="L40" s="31">
+      <c r="L40" s="32">
         <v>58.22</v>
       </c>
-      <c r="M40" s="31">
+      <c r="M40" s="32">
         <v>8.33</v>
       </c>
-      <c r="N40" s="31">
+      <c r="N40" s="32">
         <v>4.97</v>
       </c>
-      <c r="O40" s="31">
+      <c r="O40" s="32">
         <v>15.36</v>
       </c>
-      <c r="P40" s="30">
+      <c r="P40" s="31">
         <v>1744.76</v>
       </c>
-      <c r="Q40" s="31">
+      <c r="Q40" s="32">
         <v>26.26</v>
       </c>
-      <c r="R40" s="31">
+      <c r="R40" s="32">
         <v>18.96</v>
       </c>
-      <c r="S40" s="31">
+      <c r="S40" s="32">
         <v>43.93</v>
       </c>
-      <c r="T40" s="30">
+      <c r="T40" s="31">
         <v>1875.94</v>
       </c>
-      <c r="U40" s="30">
+      <c r="U40" s="31">
         <v>275.25</v>
       </c>
-      <c r="V40" s="31">
+      <c r="V40" s="32">
         <v>21.46</v>
       </c>
-      <c r="W40" s="32"/>
-      <c r="X40" s="32"/>
-      <c r="Y40" s="32"/>
-      <c r="Z40" s="32"/>
-      <c r="AA40" s="32"/>
-      <c r="AB40" s="32"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="33"/>
+      <c r="Y40" s="33"/>
+      <c r="Z40" s="33"/>
+      <c r="AA40" s="33"/>
+      <c r="AB40" s="33"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>449</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="30" t="s">
+        <v>450</v>
+      </c>
+      <c r="B41" s="32">
         <v>2.58</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>2.38</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>2.07</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>1.77</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>1.46</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>1.35</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>1.78</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>2.5</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>3.34</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>5.65</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="32">
         <v>13.71</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="32">
         <v>13.89</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="32">
         <v>16.9</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="32">
         <v>30.88</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="32">
         <v>51.41</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="32">
         <v>50.22</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>55.67</v>
       </c>
-      <c r="S41" s="30">
+      <c r="S41" s="31">
         <v>341.99</v>
       </c>
-      <c r="T41" s="32"/>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
-      <c r="W41" s="32"/>
-      <c r="X41" s="32"/>
-      <c r="Y41" s="32"/>
-      <c r="Z41" s="32"/>
-      <c r="AA41" s="32"/>
-      <c r="AB41" s="32"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="33"/>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="33"/>
+      <c r="Y41" s="33"/>
+      <c r="Z41" s="33"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="27" t="s">
-        <v>450</v>
-      </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="28"/>
-      <c r="X42" s="28"/>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="28"/>
-      <c r="AB42" s="28"/>
+      <c r="A42" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+      <c r="W42" s="29"/>
+      <c r="X42" s="29"/>
+      <c r="Y42" s="29"/>
+      <c r="Z42" s="29"/>
+      <c r="AA42" s="29"/>
+      <c r="AB42" s="29"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>451</v>
-      </c>
-      <c r="B43" s="31">
+      <c r="A43" s="30" t="s">
+        <v>452</v>
+      </c>
+      <c r="B43" s="32">
         <v>0.39</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="32">
         <v>0.38</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="32">
         <v>0.42</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="32">
         <v>0.47</v>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="32">
         <v>0.6</v>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="32">
         <v>0.25</v>
       </c>
-      <c r="H43" s="31">
+      <c r="H43" s="32">
         <v>0.21</v>
       </c>
-      <c r="I43" s="31">
+      <c r="I43" s="32">
         <v>0.21</v>
       </c>
-      <c r="J43" s="31">
+      <c r="J43" s="32">
         <v>0.22</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="32">
         <v>0.5</v>
       </c>
-      <c r="L43" s="31">
+      <c r="L43" s="32">
         <v>0.61</v>
       </c>
-      <c r="M43" s="31">
+      <c r="M43" s="32">
         <v>0.21</v>
       </c>
-      <c r="N43" s="31">
+      <c r="N43" s="32">
         <v>0.17</v>
       </c>
-      <c r="O43" s="31">
+      <c r="O43" s="32">
         <v>0.03</v>
       </c>
-      <c r="P43" s="31">
+      <c r="P43" s="32">
         <v>0.37</v>
       </c>
-      <c r="Q43" s="31">
+      <c r="Q43" s="32">
         <v>0.64</v>
       </c>
-      <c r="R43" s="31">
+      <c r="R43" s="32">
         <v>0.5</v>
       </c>
-      <c r="S43" s="31">
+      <c r="S43" s="32">
         <v>1.1</v>
       </c>
-      <c r="T43" s="31">
+      <c r="T43" s="32">
         <v>1.52</v>
       </c>
-      <c r="U43" s="31">
+      <c r="U43" s="32">
         <v>1.07</v>
       </c>
-      <c r="V43" s="31">
+      <c r="V43" s="32">
         <v>0.34</v>
       </c>
-      <c r="W43" s="31">
+      <c r="W43" s="32">
         <v>0.37</v>
       </c>
-      <c r="X43" s="31">
+      <c r="X43" s="32">
         <v>0.07</v>
       </c>
-      <c r="Y43" s="31">
+      <c r="Y43" s="32">
         <v>0.15</v>
       </c>
-      <c r="Z43" s="31">
+      <c r="Z43" s="32">
         <v>0.1</v>
       </c>
-      <c r="AA43" s="31">
+      <c r="AA43" s="32">
         <v>0.75</v>
       </c>
-      <c r="AB43" s="31">
+      <c r="AB43" s="32">
         <v>0.31</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>452</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="30" t="s">
+        <v>453</v>
+      </c>
+      <c r="B44" s="32">
         <v>0.44</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>0.41</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>0.38</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>0.33</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>0.28</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.27</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.33</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>0.29</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>0.27</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>0.08</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>0.09</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>0.1</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.11</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.15</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.74</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.92</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.91</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.91</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>0.57</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>0.23</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>0.1</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>0.34</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>0.32</v>
       </c>
-      <c r="Y44" s="32"/>
-      <c r="Z44" s="32"/>
-      <c r="AA44" s="32"/>
-      <c r="AB44" s="32"/>
+      <c r="Y44" s="33"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
+      <c r="AB44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="27" t="s">
-        <v>453</v>
-      </c>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="28"/>
-      <c r="S45" s="28"/>
-      <c r="T45" s="28"/>
-      <c r="U45" s="28"/>
-      <c r="V45" s="28"/>
-      <c r="W45" s="28"/>
-      <c r="X45" s="28"/>
-      <c r="Y45" s="28"/>
-      <c r="Z45" s="28"/>
-      <c r="AA45" s="28"/>
-      <c r="AB45" s="28"/>
+      <c r="A45" s="28" t="s">
+        <v>454</v>
+      </c>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+      <c r="T45" s="29"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+      <c r="W45" s="29"/>
+      <c r="X45" s="29"/>
+      <c r="Y45" s="29"/>
+      <c r="Z45" s="29"/>
+      <c r="AA45" s="29"/>
+      <c r="AB45" s="29"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>454</v>
-      </c>
-      <c r="B46" s="32"/>
-      <c r="C46" s="31">
+      <c r="A46" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B46" s="33"/>
+      <c r="C46" s="32">
         <v>4.04</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="32">
         <v>16.9</v>
       </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="31">
+      <c r="E46" s="33"/>
+      <c r="F46" s="32">
         <v>29.33</v>
       </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="31">
+      <c r="G46" s="33"/>
+      <c r="H46" s="32">
         <v>37.43</v>
       </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
-      <c r="N46" s="31">
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="32">
         <v>3.48</v>
       </c>
-      <c r="O46" s="32"/>
-      <c r="P46" s="31">
+      <c r="O46" s="33"/>
+      <c r="P46" s="32">
         <v>5.61</v>
       </c>
-      <c r="Q46" s="31">
+      <c r="Q46" s="32">
         <v>16.83</v>
       </c>
-      <c r="R46" s="31">
+      <c r="R46" s="32">
         <v>9.85</v>
       </c>
-      <c r="S46" s="31">
+      <c r="S46" s="32">
         <v>23.48</v>
       </c>
-      <c r="T46" s="32"/>
-      <c r="U46" s="32"/>
-      <c r="V46" s="32"/>
-      <c r="W46" s="32"/>
-      <c r="X46" s="32"/>
-      <c r="Y46" s="32"/>
-      <c r="Z46" s="32"/>
-      <c r="AA46" s="32"/>
-      <c r="AB46" s="32"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="33"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>455</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="B47" s="32">
         <v>19.54</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <v>17.55</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="31">
         <v>170.84</v>
       </c>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
-      <c r="P47" s="31">
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="32">
         <v>18.69</v>
       </c>
-      <c r="Q47" s="31">
+      <c r="Q47" s="32">
         <v>55.32</v>
       </c>
-      <c r="R47" s="30">
+      <c r="R47" s="31">
         <v>628.56</v>
       </c>
-      <c r="S47" s="32"/>
-      <c r="T47" s="32"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="32"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="32"/>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="32"/>
-      <c r="AA47" s="32"/>
-      <c r="AB47" s="32"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="33"/>
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="28"/>
-      <c r="S48" s="28"/>
-      <c r="T48" s="28"/>
-      <c r="U48" s="28"/>
-      <c r="V48" s="28"/>
-      <c r="W48" s="28"/>
-      <c r="X48" s="28"/>
-      <c r="Y48" s="28"/>
-      <c r="Z48" s="28"/>
-      <c r="AA48" s="28"/>
-      <c r="AB48" s="28"/>
+      <c r="A48" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
+      <c r="W48" s="29"/>
+      <c r="X48" s="29"/>
+      <c r="Y48" s="29"/>
+      <c r="Z48" s="29"/>
+      <c r="AA48" s="29"/>
+      <c r="AB48" s="29"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>457</v>
-      </c>
-      <c r="B49" s="31">
+      <c r="A49" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="B49" s="32">
         <v>6.12</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="32">
         <v>7.55</v>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="32">
         <v>11.21</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="32">
         <v>67.62</v>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="32">
         <v>15.14</v>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="32">
         <v>5.56</v>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="32">
         <v>14.32</v>
       </c>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="31">
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="32">
         <v>31.52</v>
       </c>
-      <c r="M49" s="31">
+      <c r="M49" s="32">
         <v>7.88</v>
       </c>
-      <c r="N49" s="31">
+      <c r="N49" s="32">
         <v>5.1</v>
       </c>
-      <c r="O49" s="31">
+      <c r="O49" s="32">
         <v>0.98</v>
       </c>
-      <c r="P49" s="31">
+      <c r="P49" s="32">
         <v>8.28</v>
       </c>
-      <c r="Q49" s="31">
+      <c r="Q49" s="32">
         <v>17.38</v>
       </c>
-      <c r="R49" s="31">
+      <c r="R49" s="32">
         <v>6.54</v>
       </c>
-      <c r="S49" s="31">
+      <c r="S49" s="32">
         <v>5.73</v>
       </c>
-      <c r="T49" s="31">
+      <c r="T49" s="32">
         <v>22.89</v>
       </c>
-      <c r="U49" s="32"/>
-      <c r="V49" s="32"/>
-      <c r="W49" s="32"/>
-      <c r="X49" s="31">
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="32">
         <v>30.7</v>
       </c>
-      <c r="Y49" s="32"/>
-      <c r="Z49" s="32"/>
-      <c r="AA49" s="32"/>
-      <c r="AB49" s="32"/>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="B50" s="32">
         <v>10.69</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>10.96</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>12.7</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>16.92</v>
       </c>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="30">
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="31">
         <v>147.17</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>3.53</v>
       </c>
-      <c r="L50" s="31">
+      <c r="L50" s="32">
         <v>3.25</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="32">
         <v>3.53</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>3.51</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>3.89</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>9.29</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>12.5</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>14.08</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>20.65</v>
       </c>
-      <c r="T50" s="32"/>
-      <c r="U50" s="32"/>
-      <c r="V50" s="32"/>
-      <c r="W50" s="32"/>
-      <c r="X50" s="32"/>
-      <c r="Y50" s="32"/>
-      <c r="Z50" s="32"/>
-      <c r="AA50" s="32"/>
-      <c r="AB50" s="32"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
+      <c r="V50" s="33"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="33"/>
+      <c r="Y50" s="33"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
+      <c r="AB50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="27" t="s">
-        <v>459</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="28"/>
-      <c r="S51" s="28"/>
-      <c r="T51" s="28"/>
-      <c r="U51" s="28"/>
-      <c r="V51" s="28"/>
-      <c r="W51" s="28"/>
-      <c r="X51" s="28"/>
-      <c r="Y51" s="28"/>
-      <c r="Z51" s="28"/>
-      <c r="AA51" s="28"/>
-      <c r="AB51" s="28"/>
+      <c r="A51" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="29"/>
+      <c r="U51" s="29"/>
+      <c r="V51" s="29"/>
+      <c r="W51" s="29"/>
+      <c r="X51" s="29"/>
+      <c r="Y51" s="29"/>
+      <c r="Z51" s="29"/>
+      <c r="AA51" s="29"/>
+      <c r="AB51" s="29"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>460</v>
-      </c>
-      <c r="B52" s="31">
+      <c r="A52" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="B52" s="32">
         <v>16.95</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="32">
         <v>23.36</v>
       </c>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="31">
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="32">
         <v>12.53</v>
       </c>
-      <c r="N52" s="31">
+      <c r="N52" s="32">
         <v>7.38</v>
       </c>
-      <c r="O52" s="31">
+      <c r="O52" s="32">
         <v>2.75</v>
       </c>
-      <c r="P52" s="32"/>
-      <c r="Q52" s="31">
+      <c r="P52" s="33"/>
+      <c r="Q52" s="32">
         <v>21.5</v>
       </c>
-      <c r="R52" s="31">
+      <c r="R52" s="32">
         <v>8.15</v>
       </c>
-      <c r="S52" s="31">
+      <c r="S52" s="32">
         <v>8.42</v>
       </c>
-      <c r="T52" s="31">
+      <c r="T52" s="32">
         <v>32.45</v>
       </c>
-      <c r="U52" s="32"/>
-      <c r="V52" s="32"/>
-      <c r="W52" s="32"/>
-      <c r="X52" s="32"/>
-      <c r="Y52" s="32"/>
-      <c r="Z52" s="32"/>
-      <c r="AA52" s="32"/>
-      <c r="AB52" s="32"/>
+      <c r="U52" s="33"/>
+      <c r="V52" s="33"/>
+      <c r="W52" s="33"/>
+      <c r="X52" s="33"/>
+      <c r="Y52" s="33"/>
+      <c r="Z52" s="33"/>
+      <c r="AA52" s="33"/>
+      <c r="AB52" s="33"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="B53" s="30">
+      <c r="A53" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="B53" s="31">
         <v>194.73</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="31">
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="32">
         <v>11.27</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="32">
         <v>12.64</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="32">
         <v>11.55</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>10.49</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="32">
         <v>10.1</v>
       </c>
-      <c r="P53" s="31">
+      <c r="P53" s="32">
         <v>20.4</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="32">
         <v>19.47</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="32">
         <v>25.15</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="32">
         <v>51.54</v>
       </c>
-      <c r="T53" s="32"/>
-      <c r="U53" s="32"/>
-      <c r="V53" s="32"/>
-      <c r="W53" s="32"/>
-      <c r="X53" s="32"/>
-      <c r="Y53" s="32"/>
-      <c r="Z53" s="32"/>
-      <c r="AA53" s="32"/>
-      <c r="AB53" s="32"/>
+      <c r="T53" s="33"/>
+      <c r="U53" s="33"/>
+      <c r="V53" s="33"/>
+      <c r="W53" s="33"/>
+      <c r="X53" s="33"/>
+      <c r="Y53" s="33"/>
+      <c r="Z53" s="33"/>
+      <c r="AA53" s="33"/>
+      <c r="AB53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="27" t="s">
-        <v>462</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="28"/>
-      <c r="R54" s="28"/>
-      <c r="S54" s="28"/>
-      <c r="T54" s="28"/>
-      <c r="U54" s="28"/>
-      <c r="V54" s="28"/>
-      <c r="W54" s="28"/>
-      <c r="X54" s="28"/>
-      <c r="Y54" s="28"/>
-      <c r="Z54" s="28"/>
-      <c r="AA54" s="28"/>
-      <c r="AB54" s="28"/>
+      <c r="A54" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
+      <c r="S54" s="29"/>
+      <c r="T54" s="29"/>
+      <c r="U54" s="29"/>
+      <c r="V54" s="29"/>
+      <c r="W54" s="29"/>
+      <c r="X54" s="29"/>
+      <c r="Y54" s="29"/>
+      <c r="Z54" s="29"/>
+      <c r="AA54" s="29"/>
+      <c r="AB54" s="29"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>463</v>
-      </c>
-      <c r="B55" s="31">
+      <c r="A55" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="B55" s="32">
         <v>12.93</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="32">
         <v>23.17</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="31">
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="32">
         <v>13.13</v>
       </c>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="31">
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="33"/>
+      <c r="L55" s="32">
         <v>90.16</v>
       </c>
-      <c r="M55" s="31">
+      <c r="M55" s="32">
         <v>11.66</v>
       </c>
-      <c r="N55" s="31">
+      <c r="N55" s="32">
         <v>7.38</v>
       </c>
-      <c r="O55" s="31">
+      <c r="O55" s="32">
         <v>1.78</v>
       </c>
-      <c r="P55" s="31">
+      <c r="P55" s="32">
         <v>8.9</v>
       </c>
-      <c r="Q55" s="31">
+      <c r="Q55" s="32">
         <v>23.91</v>
       </c>
-      <c r="R55" s="31">
+      <c r="R55" s="32">
         <v>7.2</v>
       </c>
-      <c r="S55" s="31">
+      <c r="S55" s="32">
         <v>5.9</v>
       </c>
-      <c r="T55" s="31">
+      <c r="T55" s="32">
         <v>27.38</v>
       </c>
-      <c r="U55" s="32"/>
-      <c r="V55" s="32"/>
-      <c r="W55" s="32"/>
-      <c r="X55" s="32"/>
-      <c r="Y55" s="32"/>
-      <c r="Z55" s="32"/>
-      <c r="AA55" s="32"/>
-      <c r="AB55" s="32"/>
+      <c r="U55" s="33"/>
+      <c r="V55" s="33"/>
+      <c r="W55" s="33"/>
+      <c r="X55" s="33"/>
+      <c r="Y55" s="33"/>
+      <c r="Z55" s="33"/>
+      <c r="AA55" s="33"/>
+      <c r="AB55" s="33"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>464</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="B56" s="32">
         <v>0.99</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>0.91</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>0.79</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>0.71</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>0.62</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>0.56</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <v>0.55</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>0.61</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>0.61</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>0.66</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="32">
         <v>0.86</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>1.24</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>1.8</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="32">
         <v>3.9</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>14.27</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>16.11</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="32">
         <v>18.72</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="32">
         <v>25.08</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>30.63</v>
       </c>
-      <c r="U56" s="32"/>
-      <c r="V56" s="32"/>
-      <c r="W56" s="31">
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
+      <c r="W56" s="32">
         <v>4.18</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>2.38</v>
       </c>
-      <c r="Y56" s="32"/>
-      <c r="Z56" s="32"/>
-      <c r="AA56" s="32"/>
-      <c r="AB56" s="32"/>
+      <c r="Y56" s="33"/>
+      <c r="Z56" s="33"/>
+      <c r="AA56" s="33"/>
+      <c r="AB56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="27" t="s">
-        <v>465</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
-      <c r="Q57" s="28"/>
-      <c r="R57" s="28"/>
-      <c r="S57" s="28"/>
-      <c r="T57" s="28"/>
-      <c r="U57" s="28"/>
-      <c r="V57" s="28"/>
-      <c r="W57" s="28"/>
-      <c r="X57" s="28"/>
-      <c r="Y57" s="28"/>
-      <c r="Z57" s="28"/>
-      <c r="AA57" s="28"/>
-      <c r="AB57" s="28"/>
+      <c r="A57" s="28" t="s">
+        <v>466</v>
+      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
+      <c r="U57" s="29"/>
+      <c r="V57" s="29"/>
+      <c r="W57" s="29"/>
+      <c r="X57" s="29"/>
+      <c r="Y57" s="29"/>
+      <c r="Z57" s="29"/>
+      <c r="AA57" s="29"/>
+      <c r="AB57" s="29"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>466</v>
-      </c>
-      <c r="B58" s="31">
+      <c r="A58" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="B58" s="32">
         <v>0.43</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="32">
         <v>0.02</v>
       </c>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="35">
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="33"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
+      <c r="M58" s="36">
         <v>-0.64</v>
       </c>
-      <c r="N58" s="35">
+      <c r="N58" s="36">
         <v>-0.1</v>
       </c>
-      <c r="O58" s="31">
+      <c r="O58" s="32">
         <v>0.01</v>
       </c>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="35">
+      <c r="P58" s="33"/>
+      <c r="Q58" s="36">
         <v>-0.39</v>
       </c>
-      <c r="R58" s="35">
+      <c r="R58" s="36">
         <v>-0.16</v>
       </c>
-      <c r="S58" s="31">
+      <c r="S58" s="32">
         <v>0.03</v>
       </c>
-      <c r="T58" s="31">
+      <c r="T58" s="32">
         <v>0.2</v>
       </c>
-      <c r="U58" s="32"/>
-      <c r="V58" s="32"/>
-      <c r="W58" s="32"/>
-      <c r="X58" s="32"/>
-      <c r="Y58" s="32"/>
-      <c r="Z58" s="32"/>
-      <c r="AA58" s="32"/>
-      <c r="AB58" s="32"/>
+      <c r="U58" s="33"/>
+      <c r="V58" s="33"/>
+      <c r="W58" s="33"/>
+      <c r="X58" s="33"/>
+      <c r="Y58" s="33"/>
+      <c r="Z58" s="33"/>
+      <c r="AA58" s="33"/>
+      <c r="AB58" s="33"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-      <c r="M59" s="35">
+      <c r="A59" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="36">
         <v>-1.1</v>
       </c>
-      <c r="N59" s="35">
+      <c r="N59" s="36">
         <v>-0.56</v>
       </c>
-      <c r="O59" s="31">
+      <c r="O59" s="32">
         <v>0.28</v>
       </c>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="32"/>
-      <c r="S59" s="32"/>
-      <c r="T59" s="32"/>
-      <c r="U59" s="32"/>
-      <c r="V59" s="32"/>
-      <c r="W59" s="32"/>
-      <c r="X59" s="32"/>
-      <c r="Y59" s="32"/>
-      <c r="Z59" s="32"/>
-      <c r="AA59" s="32"/>
-      <c r="AB59" s="32"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
+      <c r="R59" s="33"/>
+      <c r="S59" s="33"/>
+      <c r="T59" s="33"/>
+      <c r="U59" s="33"/>
+      <c r="V59" s="33"/>
+      <c r="W59" s="33"/>
+      <c r="X59" s="33"/>
+      <c r="Y59" s="33"/>
+      <c r="Z59" s="33"/>
+      <c r="AA59" s="33"/>
+      <c r="AB59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="28"/>
-      <c r="N60" s="28"/>
-      <c r="O60" s="28"/>
-      <c r="P60" s="28"/>
-      <c r="Q60" s="28"/>
-      <c r="R60" s="28"/>
-      <c r="S60" s="28"/>
-      <c r="T60" s="28"/>
-      <c r="U60" s="28"/>
-      <c r="V60" s="28"/>
-      <c r="W60" s="28"/>
-      <c r="X60" s="28"/>
-      <c r="Y60" s="28"/>
-      <c r="Z60" s="28"/>
-      <c r="AA60" s="28"/>
-      <c r="AB60" s="28"/>
+      <c r="A60" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+      <c r="T60" s="29"/>
+      <c r="U60" s="29"/>
+      <c r="V60" s="29"/>
+      <c r="W60" s="29"/>
+      <c r="X60" s="29"/>
+      <c r="Y60" s="29"/>
+      <c r="Z60" s="29"/>
+      <c r="AA60" s="29"/>
+      <c r="AB60" s="29"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>469</v>
-      </c>
-      <c r="B61" s="31">
+      <c r="A61" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="B61" s="32">
         <v>0.36</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="32">
         <v>0.34</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D61" s="32">
         <v>0.44</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E61" s="32">
         <v>0.5</v>
       </c>
-      <c r="F61" s="31">
+      <c r="F61" s="32">
         <v>0.56</v>
       </c>
-      <c r="G61" s="31">
+      <c r="G61" s="32">
         <v>0.37</v>
       </c>
-      <c r="H61" s="31">
+      <c r="H61" s="32">
         <v>0.17</v>
       </c>
-      <c r="I61" s="31">
+      <c r="I61" s="32">
         <v>0.19</v>
       </c>
-      <c r="J61" s="31">
+      <c r="J61" s="32">
         <v>0.19</v>
       </c>
-      <c r="K61" s="31">
+      <c r="K61" s="32">
         <v>0.42</v>
       </c>
-      <c r="L61" s="31">
+      <c r="L61" s="32">
         <v>0.89</v>
       </c>
-      <c r="M61" s="31">
+      <c r="M61" s="32">
         <v>0.28</v>
       </c>
-      <c r="N61" s="31">
+      <c r="N61" s="32">
         <v>0.2</v>
       </c>
-      <c r="O61" s="31">
+      <c r="O61" s="32">
         <v>0.33</v>
       </c>
-      <c r="P61" s="31">
+      <c r="P61" s="32">
         <v>0.63</v>
       </c>
-      <c r="Q61" s="31">
+      <c r="Q61" s="32">
         <v>0.47</v>
       </c>
-      <c r="R61" s="31">
+      <c r="R61" s="32">
         <v>0.39</v>
       </c>
-      <c r="S61" s="31">
+      <c r="S61" s="32">
         <v>1.09</v>
       </c>
-      <c r="T61" s="31">
+      <c r="T61" s="32">
         <v>1.62</v>
       </c>
-      <c r="U61" s="31">
+      <c r="U61" s="32">
         <v>1.16</v>
       </c>
-      <c r="V61" s="31">
+      <c r="V61" s="32">
         <v>0.32</v>
       </c>
-      <c r="W61" s="31">
+      <c r="W61" s="32">
         <v>0.5</v>
       </c>
-      <c r="X61" s="31">
+      <c r="X61" s="32">
         <v>0.01</v>
       </c>
-      <c r="Y61" s="31">
+      <c r="Y61" s="32">
         <v>0.22</v>
       </c>
-      <c r="Z61" s="31">
+      <c r="Z61" s="32">
         <v>0.17</v>
       </c>
-      <c r="AA61" s="31">
+      <c r="AA61" s="32">
         <v>0.83</v>
       </c>
-      <c r="AB61" s="31">
+      <c r="AB61" s="32">
         <v>0.38</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>470</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="B62" s="32">
         <v>0.43</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>0.44</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>0.42</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>0.35</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>0.28</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>0.27</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.38</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>0.35</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>0.32</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.33</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.36</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>0.33</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.35</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.5</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.73</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.81</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.9</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>1.1</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>0.92</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>0.42</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>0.22</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>0.34</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>0.34</v>
       </c>
-      <c r="Y62" s="32"/>
-      <c r="Z62" s="32"/>
-      <c r="AA62" s="32"/>
-      <c r="AB62" s="32"/>
+      <c r="Y62" s="33"/>
+      <c r="Z62" s="33"/>
+      <c r="AA62" s="33"/>
+      <c r="AB62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="27" t="s">
-        <v>471</v>
-      </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="28"/>
-      <c r="K63" s="28"/>
-      <c r="L63" s="28"/>
-      <c r="M63" s="28"/>
-      <c r="N63" s="28"/>
-      <c r="O63" s="28"/>
-      <c r="P63" s="28"/>
-      <c r="Q63" s="28"/>
-      <c r="R63" s="28"/>
-      <c r="S63" s="28"/>
-      <c r="T63" s="28"/>
-      <c r="U63" s="28"/>
-      <c r="V63" s="28"/>
-      <c r="W63" s="28"/>
-      <c r="X63" s="28"/>
-      <c r="Y63" s="28"/>
-      <c r="Z63" s="28"/>
-      <c r="AA63" s="28"/>
-      <c r="AB63" s="28"/>
+      <c r="A63" s="28" t="s">
+        <v>472</v>
+      </c>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="29"/>
+      <c r="P63" s="29"/>
+      <c r="Q63" s="29"/>
+      <c r="R63" s="29"/>
+      <c r="S63" s="29"/>
+      <c r="T63" s="29"/>
+      <c r="U63" s="29"/>
+      <c r="V63" s="29"/>
+      <c r="W63" s="29"/>
+      <c r="X63" s="29"/>
+      <c r="Y63" s="29"/>
+      <c r="Z63" s="29"/>
+      <c r="AA63" s="29"/>
+      <c r="AB63" s="29"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>472</v>
-      </c>
-      <c r="B64" s="31">
+      <c r="A64" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="B64" s="32">
         <v>4.88</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="32">
         <v>6.71</v>
       </c>
-      <c r="D64" s="31">
+      <c r="D64" s="32">
         <v>10.05</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="32">
         <v>38.27</v>
       </c>
-      <c r="F64" s="31">
+      <c r="F64" s="32">
         <v>11.19</v>
       </c>
-      <c r="G64" s="31">
+      <c r="G64" s="32">
         <v>7.06</v>
       </c>
-      <c r="H64" s="31">
+      <c r="H64" s="32">
         <v>3.78</v>
       </c>
-      <c r="I64" s="31">
+      <c r="I64" s="32">
         <v>26.84</v>
       </c>
-      <c r="J64" s="32"/>
-      <c r="K64" s="31">
+      <c r="J64" s="33"/>
+      <c r="K64" s="32">
         <v>98.33</v>
       </c>
-      <c r="L64" s="31">
+      <c r="L64" s="32">
         <v>25.14</v>
       </c>
-      <c r="M64" s="31">
+      <c r="M64" s="32">
         <v>7.89</v>
       </c>
-      <c r="N64" s="31">
+      <c r="N64" s="32">
         <v>5.68</v>
       </c>
-      <c r="O64" s="31">
+      <c r="O64" s="32">
         <v>10.15</v>
       </c>
-      <c r="P64" s="31">
+      <c r="P64" s="32">
         <v>4.54</v>
       </c>
-      <c r="Q64" s="31">
+      <c r="Q64" s="32">
         <v>9.65</v>
       </c>
-      <c r="R64" s="31">
+      <c r="R64" s="32">
         <v>5.25</v>
       </c>
-      <c r="S64" s="31">
+      <c r="S64" s="32">
         <v>12.28</v>
       </c>
-      <c r="T64" s="31">
+      <c r="T64" s="32">
         <v>28.52</v>
       </c>
-      <c r="U64" s="32"/>
-      <c r="V64" s="32"/>
-      <c r="W64" s="30">
+      <c r="U64" s="33"/>
+      <c r="V64" s="33"/>
+      <c r="W64" s="31">
         <v>166.35</v>
       </c>
-      <c r="X64" s="32"/>
-      <c r="Y64" s="32"/>
-      <c r="Z64" s="32"/>
-      <c r="AA64" s="32"/>
-      <c r="AB64" s="32"/>
+      <c r="X64" s="33"/>
+      <c r="Y64" s="33"/>
+      <c r="Z64" s="33"/>
+      <c r="AA64" s="33"/>
+      <c r="AB64" s="33"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>473</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="B65" s="32">
         <v>8.89</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>10.35</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>10.4</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>11.49</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>11.53</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>17.37</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>26.61</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>16.19</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>11.52</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>10.41</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>7.55</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="32">
         <v>6.71</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>6.26</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>7.16</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>7.85</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>14.38</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="32">
         <v>17.24</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>30.42</v>
       </c>
-      <c r="T65" s="30">
+      <c r="T65" s="31">
         <v>1407.98</v>
       </c>
-      <c r="U65" s="32"/>
-      <c r="V65" s="32"/>
-      <c r="W65" s="32"/>
-      <c r="X65" s="32"/>
-      <c r="Y65" s="32"/>
-      <c r="Z65" s="32"/>
-      <c r="AA65" s="32"/>
-      <c r="AB65" s="32"/>
+      <c r="U65" s="33"/>
+      <c r="V65" s="33"/>
+      <c r="W65" s="33"/>
+      <c r="X65" s="33"/>
+      <c r="Y65" s="33"/>
+      <c r="Z65" s="33"/>
+      <c r="AA65" s="33"/>
+      <c r="AB65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="27" t="s">
-        <v>474</v>
-      </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28"/>
-      <c r="J66" s="28"/>
-      <c r="K66" s="28"/>
-      <c r="L66" s="28"/>
-      <c r="M66" s="28"/>
-      <c r="N66" s="28"/>
-      <c r="O66" s="28"/>
-      <c r="P66" s="28"/>
-      <c r="Q66" s="28"/>
-      <c r="R66" s="28"/>
-      <c r="S66" s="28"/>
-      <c r="T66" s="28"/>
-      <c r="U66" s="28"/>
-      <c r="V66" s="28"/>
-      <c r="W66" s="28"/>
-      <c r="X66" s="28"/>
-      <c r="Y66" s="28"/>
-      <c r="Z66" s="28"/>
-      <c r="AA66" s="28"/>
-      <c r="AB66" s="28"/>
+      <c r="A66" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29"/>
+      <c r="M66" s="29"/>
+      <c r="N66" s="29"/>
+      <c r="O66" s="29"/>
+      <c r="P66" s="29"/>
+      <c r="Q66" s="29"/>
+      <c r="R66" s="29"/>
+      <c r="S66" s="29"/>
+      <c r="T66" s="29"/>
+      <c r="U66" s="29"/>
+      <c r="V66" s="29"/>
+      <c r="W66" s="29"/>
+      <c r="X66" s="29"/>
+      <c r="Y66" s="29"/>
+      <c r="Z66" s="29"/>
+      <c r="AA66" s="29"/>
+      <c r="AB66" s="29"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="B67" s="32"/>
-      <c r="C67" s="31">
+      <c r="A67" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="B67" s="33"/>
+      <c r="C67" s="32">
         <v>3.08</v>
       </c>
-      <c r="D67" s="31">
+      <c r="D67" s="32">
         <v>7.39</v>
       </c>
-      <c r="E67" s="31">
+      <c r="E67" s="32">
         <v>58.46</v>
       </c>
-      <c r="F67" s="31">
+      <c r="F67" s="32">
         <v>24.49</v>
       </c>
-      <c r="G67" s="31">
+      <c r="G67" s="32">
         <v>4.99</v>
       </c>
-      <c r="H67" s="31">
+      <c r="H67" s="32">
         <v>21.76</v>
       </c>
-      <c r="I67" s="32">
+      <c r="I67" s="33">
         <v>21679.37</v>
       </c>
-      <c r="J67" s="32"/>
-      <c r="K67" s="31">
+      <c r="J67" s="33"/>
+      <c r="K67" s="32">
         <v>83.45</v>
       </c>
-      <c r="L67" s="32"/>
-      <c r="M67" s="32"/>
-      <c r="N67" s="31">
+      <c r="L67" s="33"/>
+      <c r="M67" s="33"/>
+      <c r="N67" s="32">
         <v>3.72</v>
       </c>
-      <c r="O67" s="32"/>
-      <c r="P67" s="31">
+      <c r="O67" s="33"/>
+      <c r="P67" s="32">
         <v>8.46</v>
       </c>
-      <c r="Q67" s="31">
+      <c r="Q67" s="32">
         <v>9.37</v>
       </c>
-      <c r="R67" s="31">
+      <c r="R67" s="32">
         <v>5.94</v>
       </c>
-      <c r="S67" s="31">
+      <c r="S67" s="32">
         <v>19.37</v>
       </c>
-      <c r="T67" s="32"/>
-      <c r="U67" s="32"/>
-      <c r="V67" s="32"/>
-      <c r="W67" s="32"/>
-      <c r="X67" s="32"/>
-      <c r="Y67" s="32"/>
-      <c r="Z67" s="32"/>
-      <c r="AA67" s="32"/>
-      <c r="AB67" s="32"/>
+      <c r="T67" s="33"/>
+      <c r="U67" s="33"/>
+      <c r="V67" s="33"/>
+      <c r="W67" s="33"/>
+      <c r="X67" s="33"/>
+      <c r="Y67" s="33"/>
+      <c r="Z67" s="33"/>
+      <c r="AA67" s="33"/>
+      <c r="AB67" s="33"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>476</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="B68" s="32">
         <v>11.06</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>7.45</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>12.27</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>17.54</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>16.45</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>19.98</v>
       </c>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="31">
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="32">
         <v>22.02</v>
       </c>
-      <c r="K68" s="30">
+      <c r="K68" s="31">
         <v>263.54</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="32">
         <v>34.68</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="32">
         <v>20.73</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="32">
         <v>12.78</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>27.29</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>13.52</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="32">
         <v>22.7</v>
       </c>
-      <c r="R68" s="31">
+      <c r="R68" s="32">
         <v>37.19</v>
       </c>
-      <c r="S68" s="32"/>
-      <c r="T68" s="32"/>
-      <c r="U68" s="32"/>
-      <c r="V68" s="32"/>
-      <c r="W68" s="32"/>
-      <c r="X68" s="32"/>
-      <c r="Y68" s="32"/>
-      <c r="Z68" s="32"/>
-      <c r="AA68" s="32"/>
-      <c r="AB68" s="32"/>
+      <c r="S68" s="33"/>
+      <c r="T68" s="33"/>
+      <c r="U68" s="33"/>
+      <c r="V68" s="33"/>
+      <c r="W68" s="33"/>
+      <c r="X68" s="33"/>
+      <c r="Y68" s="33"/>
+      <c r="Z68" s="33"/>
+      <c r="AA68" s="33"/>
+      <c r="AB68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="27" t="s">
-        <v>477</v>
-      </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="28"/>
-      <c r="K69" s="28"/>
-      <c r="L69" s="28"/>
-      <c r="M69" s="28"/>
-      <c r="N69" s="28"/>
-      <c r="O69" s="28"/>
-      <c r="P69" s="28"/>
-      <c r="Q69" s="28"/>
-      <c r="R69" s="28"/>
-      <c r="S69" s="28"/>
-      <c r="T69" s="28"/>
-      <c r="U69" s="28"/>
-      <c r="V69" s="28"/>
-      <c r="W69" s="28"/>
-      <c r="X69" s="28"/>
-      <c r="Y69" s="28"/>
-      <c r="Z69" s="28"/>
-      <c r="AA69" s="28"/>
-      <c r="AB69" s="28"/>
+      <c r="A69" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="29"/>
+      <c r="P69" s="29"/>
+      <c r="Q69" s="29"/>
+      <c r="R69" s="29"/>
+      <c r="S69" s="29"/>
+      <c r="T69" s="29"/>
+      <c r="U69" s="29"/>
+      <c r="V69" s="29"/>
+      <c r="W69" s="29"/>
+      <c r="X69" s="29"/>
+      <c r="Y69" s="29"/>
+      <c r="Z69" s="29"/>
+      <c r="AA69" s="29"/>
+      <c r="AB69" s="29"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
-        <v>478</v>
-      </c>
-      <c r="B70" s="32"/>
-      <c r="C70" s="31">
+      <c r="A70" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="B70" s="33"/>
+      <c r="C70" s="32">
         <v>3.65</v>
       </c>
-      <c r="D70" s="31">
+      <c r="D70" s="32">
         <v>18.02</v>
       </c>
-      <c r="E70" s="32"/>
-      <c r="F70" s="31">
+      <c r="E70" s="33"/>
+      <c r="F70" s="32">
         <v>27.76</v>
       </c>
-      <c r="G70" s="32"/>
-      <c r="H70" s="31">
+      <c r="G70" s="33"/>
+      <c r="H70" s="32">
         <v>30.63</v>
       </c>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
-      <c r="M70" s="32"/>
-      <c r="N70" s="31">
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
+      <c r="M70" s="33"/>
+      <c r="N70" s="32">
         <v>4.01</v>
       </c>
-      <c r="O70" s="32"/>
-      <c r="P70" s="31">
+      <c r="O70" s="33"/>
+      <c r="P70" s="32">
         <v>9.56</v>
       </c>
-      <c r="Q70" s="31">
+      <c r="Q70" s="32">
         <v>12.34</v>
       </c>
-      <c r="R70" s="31">
+      <c r="R70" s="32">
         <v>7.7</v>
       </c>
-      <c r="S70" s="31">
+      <c r="S70" s="32">
         <v>23.22</v>
       </c>
-      <c r="T70" s="32"/>
-      <c r="U70" s="32"/>
-      <c r="V70" s="32"/>
-      <c r="W70" s="32"/>
-      <c r="X70" s="32"/>
-      <c r="Y70" s="32"/>
-      <c r="Z70" s="32"/>
-      <c r="AA70" s="32"/>
-      <c r="AB70" s="32"/>
+      <c r="T70" s="33"/>
+      <c r="U70" s="33"/>
+      <c r="V70" s="33"/>
+      <c r="W70" s="33"/>
+      <c r="X70" s="33"/>
+      <c r="Y70" s="33"/>
+      <c r="Z70" s="33"/>
+      <c r="AA70" s="33"/>
+      <c r="AB70" s="33"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="B71" s="31">
+      <c r="A71" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="B71" s="32">
         <v>18.87</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="32">
         <v>15.51</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="32">
         <v>89.41</v>
       </c>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="31">
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
+      <c r="M71" s="32">
         <v>71.31</v>
       </c>
-      <c r="N71" s="31">
+      <c r="N71" s="32">
         <v>19.05</v>
       </c>
-      <c r="O71" s="31">
+      <c r="O71" s="32">
         <v>74.79</v>
       </c>
-      <c r="P71" s="31">
+      <c r="P71" s="32">
         <v>16.71</v>
       </c>
-      <c r="Q71" s="31">
+      <c r="Q71" s="32">
         <v>32.85</v>
       </c>
-      <c r="R71" s="31">
+      <c r="R71" s="32">
         <v>64.53</v>
       </c>
-      <c r="S71" s="32"/>
-      <c r="T71" s="32"/>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="32"/>
-      <c r="Y71" s="32"/>
-      <c r="Z71" s="32"/>
-      <c r="AA71" s="32"/>
-      <c r="AB71" s="32"/>
+      <c r="S71" s="33"/>
+      <c r="T71" s="33"/>
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="33"/>
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="33"/>
+      <c r="AA71" s="33"/>
+      <c r="AB71" s="33"/>
     </row>
     <row r="72" ht="15.75" customHeight="1"/>
     <row r="73" ht="15.75" customHeight="1"/>
